--- a/conf-data/excel/Datas/skill/skill_data.xlsx
+++ b/conf-data/excel/Datas/skill/skill_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProjectFY_wuziwei1\UnrealEngine\FYGame\Data\excel\Datas\skill\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\opensrc\c++\gameSrv\conf-data\excel\Datas\skill\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A89443C-0394-41DC-9F86-C5CAD0553CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF7F2B1-A7B9-457D-95DD-CF55B4F33E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="index" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="775">
   <si>
     <t>##var</t>
   </si>
@@ -2517,6 +2517,14 @@
 【强化战技：重雷】
 【驭雷】能量充盈时，长按战技键发动：
 逻华可对前方发动连续突刺斩击，造成大量雷元素伤害。</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>alias</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>variants</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -2797,7 +2805,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2964,6 +2972,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3627,13 +3638,13 @@
       <c r="G1" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="62" t="s">
+      <c r="H1" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="65"/>
       <c r="M1" s="18"/>
       <c r="N1" s="18"/>
     </row>
@@ -3830,17 +3841,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="25.875" customWidth="1"/>
     <col min="7" max="7" width="18.5" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="15.75" customWidth="1"/>
-    <col min="13" max="13" width="19.625" customWidth="1"/>
+    <col min="15" max="15" width="19.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
@@ -3868,15 +3879,17 @@
       <c r="I1" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="65" t="s">
+      <c r="J1" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-    </row>
-    <row r="2" spans="1:14" s="35" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+    </row>
+    <row r="2" spans="1:16" s="35" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="38" t="s">
         <v>0</v>
       </c>
@@ -3897,14 +3910,20 @@
       <c r="L2" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="39" t="s">
+      <c r="M2" s="62" t="s">
+        <v>773</v>
+      </c>
+      <c r="N2" s="62" t="s">
+        <v>774</v>
+      </c>
+      <c r="O2" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="39" t="s">
+      <c r="P2" s="39" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" s="36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="40" t="s">
         <v>11</v>
       </c>
@@ -3929,12 +3948,14 @@
       <c r="L3" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="40" t="s">
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="40"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="P3" s="40"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="18"/>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -3949,8 +3970,10 @@
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="18"/>
       <c r="B5" s="18" t="s">
         <v>97</v>
@@ -3971,23 +3994,25 @@
         <v>100</v>
       </c>
       <c r="L5" s="18"/>
-      <c r="M5" s="18" t="s">
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="N5" s="18"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="P5" s="18"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J6" t="s">
         <v>102</v>
       </c>
       <c r="K6" t="s">
         <v>77</v>
       </c>
-      <c r="M6" t="s">
+      <c r="O6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J7" s="18" t="s">
         <v>104</v>
       </c>
@@ -3995,11 +4020,13 @@
         <v>105</v>
       </c>
       <c r="L7" s="18"/>
-      <c r="M7" s="18" t="s">
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="18"/>
       <c r="B9" s="52" t="s">
         <v>107</v>
@@ -4019,11 +4046,11 @@
       <c r="K9" s="52" t="s">
         <v>110</v>
       </c>
-      <c r="M9" s="18" t="s">
+      <c r="O9" s="18" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J10" s="18" t="s">
         <v>99</v>
       </c>
@@ -4031,11 +4058,13 @@
         <v>100</v>
       </c>
       <c r="L10" s="18"/>
-      <c r="M10" s="18" t="s">
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J11" s="18" t="s">
         <v>104</v>
       </c>
@@ -4043,13 +4072,15 @@
         <v>105</v>
       </c>
       <c r="L11" s="18"/>
-      <c r="M11" s="18" t="s">
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18" t="s">
         <v>106</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="J1:P1"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
